--- a/expected_tags.xlsx
+++ b/expected_tags.xlsx
@@ -734,8 +734,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEN CLOTHING COATS FUR &amp; SHEARLING
-</t>
+          <t>MEN CLOTHING COATS FUR &amp; SHEARLING</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
